--- a/artfynd/A 49223-2024 artfynd.xlsx
+++ b/artfynd/A 49223-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150050</v>
       </c>
       <c r="B2" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49223-2024 artfynd.xlsx
+++ b/artfynd/A 49223-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150050</v>
       </c>
       <c r="B2" t="n">
-        <v>92008</v>
+        <v>92020</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49223-2024 artfynd.xlsx
+++ b/artfynd/A 49223-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150050</v>
       </c>
       <c r="B2" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49223-2024 artfynd.xlsx
+++ b/artfynd/A 49223-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121150050</v>
       </c>
       <c r="B2" t="n">
-        <v>92021</v>
+        <v>92024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
